--- a/site/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -837,154 +837,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KHB3FH2HS3R9APE8284T41M3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01KHB3FH2HS3R9APE8284T41M3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Admin Notification Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY4V4B9MPS45NWNY829Z3F</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#01K5TY4V4B9MPS45NWNY829Z3F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHB3FH2HS3R9APE8284T41M3</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01KHB3FH2HS3R9APE8284T41M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mapping Sections</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHB3AWGXPZEQS9M5QDT0X0PB</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01KHB3AWGXPZEQS9M5QDT0X0PB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Workers-and-Benefits-Sync-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>
